--- a/Data_clean/MCAS/Estados_US/Edos_USA_2018/HAWAII_2018.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2018/HAWAII_2018.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -467,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -620,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Ozumba</t>
@@ -688,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Antonio la Isla</t>
+          <t>San Antonio La Isla</t>
         </is>
       </c>
       <c r="C24">
@@ -701,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C25">
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -762,7 +877,7 @@
         <v>14</v>
       </c>
       <c r="D29">
-        <v>0.09090909090909091</v>
+        <v>0.09090909090909093</v>
       </c>
     </row>
     <row r="30">
@@ -784,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -797,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -810,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -823,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -836,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C35">
@@ -849,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Xichú</t>
@@ -862,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -875,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -895,7 +1050,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C39">
@@ -906,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C40">
@@ -919,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -932,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -945,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C43">
@@ -958,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -989,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Amatitán</t>
@@ -1002,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Ameca</t>
@@ -1015,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C48">
@@ -1028,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1041,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1054,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -1067,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>La Manzanilla de la Paz</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C52">
@@ -1080,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C53">
@@ -1093,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -1106,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Mezquitic</t>
@@ -1119,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -1132,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1202,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Pajacuarán</t>
@@ -1215,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -1241,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Villamar</t>
@@ -1267,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1280,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1311,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1342,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C72">
@@ -1355,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>La Yesca</t>
@@ -1368,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -1381,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C75">
@@ -1394,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -1407,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1420,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1433,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1453,7 +1788,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C80">
@@ -1464,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C81">
@@ -1477,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Ixpantepec Nieves</t>
@@ -1490,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C83">
@@ -1503,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C84">
@@ -1516,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C85">
@@ -1529,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>San Esteban Atatlahuca</t>
@@ -1542,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>San Juan Bautista Cuicatlán</t>
@@ -1555,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>San Juan Mixtepec - Distr. 08 -</t>
@@ -1568,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>San Miguel Coatlán</t>
@@ -1581,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -1594,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1625,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Cohetzala</t>
@@ -1638,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C94">
@@ -1651,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -1664,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C96">
@@ -1677,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mazapiltepec de Juárez</t>
+          <t>Mazapiltepec De Juárez</t>
         </is>
       </c>
       <c r="C97">
@@ -1690,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1703,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Tlachichuca</t>
@@ -1716,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1736,7 +2166,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C101">
@@ -1747,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1778,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1809,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Fronteras</t>
@@ -1822,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1853,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1884,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1915,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1946,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -1959,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -1972,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -1985,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2016,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2039,41 +2529,6 @@
       </c>
       <c r="D121">
         <v>1</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 794,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Diciembre de 2019</t>
-        </is>
       </c>
     </row>
   </sheetData>
